--- a/real_estate_forms/025_your_dream_home_checklist_form--real_estate_forms.xlsx
+++ b/real_estate_forms/025_your_dream_home_checklist_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -715,8 +715,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,12 +744,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'single_family_home'}</t>
+          <t>single_family_home</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Single Family Home'}</t>
+          <t>Single Family Home</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'4_or_more'}</t>
+          <t>4_or_more</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '4 or more'}</t>
+          <t>4 or more</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'under_200,000'}</t>
+          <t>under_200,000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Under 200,000'}</t>
+          <t>Under 200,000</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'200,000-400,000'}</t>
+          <t>200,000-400,000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '200,000-400,000'}</t>
+          <t>200,000-400,000</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'400,000_or_more'}</t>
+          <t>400,000_or_more</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '400,000 or more'}</t>
+          <t>400,000 or more</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'City'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'suburb'}</t>
+          <t>suburb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Suburb'}</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rural'}</t>
+          <t>Rural</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
